--- a/DocumentUnderstandingProcess/contentFiles/any/any/pt0/VisualBasic/Tests/Cache/ExportMergedDocuments_4-4.xlsx
+++ b/DocumentUnderstandingProcess/contentFiles/any/any/pt0/VisualBasic/Tests/Cache/ExportMergedDocuments_4-4.xlsx
@@ -88,13 +88,13 @@
     <x:t>2.95</x:t>
   </x:si>
   <x:si>
-    <x:t>Pan Fried Leek Dumplings #AT (2)</x:t>
+    <x:t>Pan Fried Leek Dumplings IAT (2)</x:t>
   </x:si>
   <x:si>
     <x:t>5.95</x:t>
   </x:si>
   <x:si>
-    <x:t>Pork Xiao Long Bao(10) ¿*/ÅË#E(10)</x:t>
+    <x:t>Pork Xiao Long Bao(10) A¥R]J¿E(10)</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -103,40 +103,40 @@
     <x:t>23.00</x:t>
   </x:si>
   <x:si>
-    <x:t>Q-BAO (5) #NEJ (5)</x:t>
+    <x:t>Q-BAO (5) WEEL (5)</x:t>
   </x:si>
   <x:si>
     <x:t>11.25</x:t>
   </x:si>
   <x:si>
-    <x:t>Chicken potstickers *'ÈPJ$3N5(6)</x:t>
+    <x:t>Chicken potstickers KR$55(6)</x:t>
   </x:si>
   <x:si>
     <x:t>4.95</x:t>
   </x:si>
   <x:si>
-    <x:t>Tomato Mushroom Steamed dumpli PEATTAMAMKE (6)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Zucchini shrimp dumplings 7U#HA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>beef stew nodle soup (Non Spicy P¿#PJHE(T#)</x:t>
+    <x:t>Tomato Mushroom Steamed dumpli pEiAINABUNXA (6)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Zucchini shrimp dumplings A/LC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>beef stew nodle soup (Non Spicy 0H#4PJB(TY)</x:t>
   </x:si>
   <x:si>
     <x:t>8.95</x:t>
   </x:si>
   <x:si>
-    <x:t>dandan noodle #2H</x:t>
-  </x:si>
-  <x:si>
-    <x:t>banana naan bread EAA#</x:t>
+    <x:t>dandan noodle INCMM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>banana naan bread BATAI</x:t>
   </x:si>
   <x:si>
     <x:t>10.50</x:t>
   </x:si>
   <x:si>
-    <x:t>house made plum juice PUMgrt</x:t>
+    <x:t>house made plum juice</x:t>
   </x:si>
   <x:si>
     <x:t>9.00</x:t>

--- a/DocumentUnderstandingProcess/contentFiles/any/any/pt0/VisualBasic/Tests/Cache/ExportMergedDocuments_4-4.xlsx
+++ b/DocumentUnderstandingProcess/contentFiles/any/any/pt0/VisualBasic/Tests/Cache/ExportMergedDocuments_4-4.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
     <x:t>Receipt Name</x:t>
   </x:si>
@@ -79,7 +79,7 @@
     <x:t>Line Amount</x:t>
   </x:si>
   <x:si>
-    <x:t>green onion Pancakes (1)</x:t>
+    <x:t>green onion Pancakes Mur4Alf (1)</x:t>
   </x:si>
   <x:si>
     <x:t>1</x:t>
@@ -88,13 +88,13 @@
     <x:t>2.95</x:t>
   </x:si>
   <x:si>
-    <x:t>Pan Fried Leek Dumplings IAT (2)</x:t>
+    <x:t>Pan Fried Leek Dumplings Ito7 (2)</x:t>
   </x:si>
   <x:si>
     <x:t>5.95</x:t>
   </x:si>
   <x:si>
-    <x:t>Pork Xiao Long Bao(10) A¥R]J¿E(10)</x:t>
+    <x:t>Pork Xiao Long Bao(10) K¥-]iN5E(10)</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -103,40 +103,40 @@
     <x:t>23.00</x:t>
   </x:si>
   <x:si>
-    <x:t>Q-BAO (5) WEEL (5)</x:t>
+    <x:t>Q-BAO (5) NELNE (5)</x:t>
   </x:si>
   <x:si>
     <x:t>11.25</x:t>
   </x:si>
   <x:si>
-    <x:t>Chicken potstickers KR$55(6)</x:t>
+    <x:t>Chicken potstickers RCI8MEl5(6)</x:t>
   </x:si>
   <x:si>
     <x:t>4.95</x:t>
   </x:si>
   <x:si>
-    <x:t>Tomato Mushroom Steamed dumpli pEiAINABUNXA (6)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Zucchini shrimp dumplings A/LC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>beef stew nodle soup (Non Spicy 0H#4PJB(TY)</x:t>
+    <x:t>Tomato Mushroom Steamed dumpli UtjAI/iABI4AKÉÑ (6)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Zucchini shrimp dumplings jJ¥EBBtEe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>beef stew nodle soup (Non Spicy</x:t>
   </x:si>
   <x:si>
     <x:t>8.95</x:t>
   </x:si>
   <x:si>
-    <x:t>dandan noodle INCMM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>banana naan bread BATAI</x:t>
+    <x:t>dandan noodle ti2ii</x:t>
+  </x:si>
+  <x:si>
+    <x:t>banana naan bread BIATEAI</x:t>
   </x:si>
   <x:si>
     <x:t>10.50</x:t>
   </x:si>
   <x:si>
-    <x:t>house made plum juice</x:t>
+    <x:t>house made plum juice tthNart</x:t>
   </x:si>
   <x:si>
     <x:t>9.00</x:t>
